--- a/media/Levels/Level_4.xlsx
+++ b/media/Levels/Level_4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ACD40FE-E641-499E-AC23-30A7FBED180D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649404B3-9296-41A6-8A04-13157FF927D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2739887D-75BF-488C-B937-CF17A666C93E}"/>
   </bookViews>
@@ -1292,10 +1292,10 @@
         <v>0</v>
       </c>
       <c r="BW1" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BX1" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BY1" s="5">
         <v>0</v>
@@ -68613,10 +68613,10 @@
         <v>0</v>
       </c>
       <c r="BW150" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BX150" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BY150" s="5">
         <v>0</v>
